--- a/Result/profitability/2002.xlsx
+++ b/Result/profitability/2002.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.02</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07375000000000001</v>
+        <v>0.09125</v>
       </c>
       <c r="N2" t="n">
-        <v>5.585</v>
+        <v>6.3025</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.24125</v>
+        <v>0.25625</v>
       </c>
       <c r="N3" t="n">
-        <v>8.455</v>
+        <v>8.828749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3725000000000001</v>
+        <v>0.38625</v>
       </c>
       <c r="N4" t="n">
-        <v>10.32625</v>
+        <v>10.6275</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.20625</v>
+        <v>0.23875</v>
       </c>
       <c r="N5" t="n">
-        <v>4.393750000000001</v>
+        <v>5.3025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.59</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1475</v>
+        <v>0.1850000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46125</v>
+        <v>3.421250000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.175</v>
+        <v>0.19375</v>
       </c>
       <c r="N7" t="n">
-        <v>2.80625</v>
+        <v>3.19625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2787500000000001</v>
+        <v>0.31625</v>
       </c>
       <c r="N8" t="n">
-        <v>5.181249999999999</v>
+        <v>5.75875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.4325</v>
       </c>
       <c r="N10" t="n">
-        <v>8.129999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.39</v>
       </c>
       <c r="N11" t="n">
-        <v>7.962499999999999</v>
+        <v>7.9625</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9361,10 +9361,10 @@
         <v>-1902</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="M71" t="n">
-        <v>0.01375</v>
+        <v>0.0125</v>
       </c>
       <c r="N71" t="n">
         <v>4.06625</v>
@@ -9394,10 +9394,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="X71" t="n">
-        <v>-7</v>
+        <v>-7.5</v>
       </c>
       <c r="Y71" t="n">
         <v>-4.86</v>
@@ -9406,10 +9406,10 @@
         <v>-0.8772563176895307</v>
       </c>
       <c r="AA71" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AB71" t="n">
-        <v>-2.333333333333333</v>
+        <v>-2.444444444444445</v>
       </c>
       <c r="AC71" t="n">
         <v>-4.36</v>
@@ -9491,7 +9491,7 @@
         <v>-0.16</v>
       </c>
       <c r="M72" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>-0.001249999999999998</v>
       </c>
       <c r="N72" t="n">
         <v>3.7175</v>
@@ -9521,10 +9521,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="X72" t="n">
-        <v>0.3333333333333335</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="Y72" t="n">
         <v>-0.41</v>
@@ -9618,7 +9618,7 @@
         <v>-0.01</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.0175</v>
+        <v>-0.01875</v>
       </c>
       <c r="N73" t="n">
         <v>3.48875</v>
@@ -9745,7 +9745,7 @@
         <v>-0.16</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.0425</v>
+        <v>-0.04375</v>
       </c>
       <c r="N74" t="n">
         <v>3.3575</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>88841</v>
+      </c>
+      <c r="D75" t="n">
+        <v>81774</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7067</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3667</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-361</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3306</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2075</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03749999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.72125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.387387387387387</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.076923076923077</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>10.69117647058824</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
